--- a/data/Supplementary_Data_S2.xlsx
+++ b/data/Supplementary_Data_S2.xlsx
@@ -752,7 +752,7 @@
     <row r="2" ht="64" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>TCGA results used in revised Figure 4 include primary SBS3 and SBS10 scores and the final exposure-trained SBS6 clinical readout. CI denotes the 95% confidence interval. Pearson-r intervals use Fisher transformation. AUC intervals use 10,000 class-stratified patient-bootstrap replicates. P values are unadjusted two-sided Pearson tests for continuous HRD and Mann–Whitney U tests for binary groups. External endpoint and MANTIS-threshold sensitivity results are in Data S3 (clinical_revision).</t>
+          <t>TCGA results used in Figure 4 use the primary SBS3, SBS6 and SBS10 scores. CIs denote 95% confidence intervals. Pearson-r intervals use Fisher transformation. AUC intervals use 10,000 class-stratified patient-bootstrap replicates. P values are unadjusted two-sided Pearson tests for continuous HRD and Mann–Whitney U tests for binary groups. External endpoint and MANTIS-threshold sensitivity results are in Data S3 (clinical_revision).</t>
         </is>
       </c>
     </row>
@@ -875,7 +875,7 @@
     <row r="7" ht="31" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>UCEC final SBS6 clinical readout for MANTIS-defined MSI</t>
+          <t>UCEC primary SBS6 score for MANTIS-defined MSI</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -895,16 +895,16 @@
         </is>
       </c>
       <c r="F7" s="6" t="n">
-        <v>0.6423618877208679</v>
+        <v>0.6186535450682173</v>
       </c>
       <c r="G7" s="6" t="n">
-        <v>0.5805552449116529</v>
+        <v>0.554907552374562</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>0.7009272720495041</v>
+        <v>0.6805720196823977</v>
       </c>
       <c r="I7" s="7" t="n">
-        <v>2.427016180643133e-05</v>
+        <v>0.0004342194440783294</v>
       </c>
     </row>
     <row r="8" ht="31" customHeight="1">
@@ -983,7 +983,7 @@
     <row r="2" ht="36" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Endpoints use TCGA out-of-fold primary SBS3/SBS10 scores and the final exposure-trained SBS6 clinical readout, with the corresponding genomic labels. HRD denotes homologous recombination deficiency. MSI denotes microsatellite instability. The MANTIS classification rule is specified below.</t>
+          <t>Endpoints use TCGA out-of-fold primary SBS3, SBS6 and SBS10 scores with the corresponding genomic labels. HRD denotes homologous recombination deficiency and MSI denotes microsatellite instability. The MANTIS classification rule is specified below.</t>
         </is>
       </c>
     </row>
@@ -16906,7 +16906,7 @@
         </is>
       </c>
       <c r="E428" s="10" t="n">
-        <v>0.5630855423011348</v>
+        <v>0.0607594558667516</v>
       </c>
       <c r="F428" s="10" t="n">
         <v>0</v>
@@ -16943,7 +16943,7 @@
         </is>
       </c>
       <c r="E429" s="6" t="n">
-        <v>-0.2074961932278009</v>
+        <v>-0.4565054908619439</v>
       </c>
       <c r="F429" s="6" t="n">
         <v>0</v>
@@ -16980,7 +16980,7 @@
         </is>
       </c>
       <c r="E430" s="10" t="n">
-        <v>0.5510352280296126</v>
+        <v>-0.1046791039914738</v>
       </c>
       <c r="F430" s="10" t="n">
         <v>0.22864754</v>
@@ -17017,7 +17017,7 @@
         </is>
       </c>
       <c r="E431" s="6" t="n">
-        <v>0.0444733303137185</v>
+        <v>-0.0454549797857355</v>
       </c>
       <c r="F431" s="6" t="n">
         <v>0.09974747</v>
@@ -17054,7 +17054,7 @@
         </is>
       </c>
       <c r="E432" s="10" t="n">
-        <v>0.5983600667311912</v>
+        <v>0.2841912026078816</v>
       </c>
       <c r="F432" s="10" t="n">
         <v>0.54763174</v>
@@ -17091,7 +17091,7 @@
         </is>
       </c>
       <c r="E433" s="6" t="n">
-        <v>0.6645590515609311</v>
+        <v>0.8798437521942101</v>
       </c>
       <c r="F433" s="6" t="n">
         <v>0.9027844</v>
@@ -17128,7 +17128,7 @@
         </is>
       </c>
       <c r="E434" s="10" t="n">
-        <v>1.902161389149563</v>
+        <v>0.6695052860306451</v>
       </c>
       <c r="F434" s="10" t="n">
         <v>0</v>
@@ -17165,7 +17165,7 @@
         </is>
       </c>
       <c r="E435" s="6" t="n">
-        <v>-0.1077316515008281</v>
+        <v>-0.0342141511916494</v>
       </c>
       <c r="F435" s="6" t="n">
         <v>0.111196406</v>
@@ -17202,7 +17202,7 @@
         </is>
       </c>
       <c r="E436" s="10" t="n">
-        <v>0.9394661218750168</v>
+        <v>1.044034995065433</v>
       </c>
       <c r="F436" s="10" t="n">
         <v>0.0997455</v>
@@ -17239,7 +17239,7 @@
         </is>
       </c>
       <c r="E437" s="6" t="n">
-        <v>0.1647596000667252</v>
+        <v>-0.363804279459305</v>
       </c>
       <c r="F437" s="6" t="n">
         <v>0</v>
@@ -17276,7 +17276,7 @@
         </is>
       </c>
       <c r="E438" s="10" t="n">
-        <v>0.0857339071869677</v>
+        <v>-0.4974136753922611</v>
       </c>
       <c r="F438" s="10" t="n">
         <v>0</v>
@@ -17313,7 +17313,7 @@
         </is>
       </c>
       <c r="E439" s="6" t="n">
-        <v>-0.6709167579001815</v>
+        <v>-1.113117844516696</v>
       </c>
       <c r="F439" s="6" t="n">
         <v>0.07912378</v>
@@ -17350,7 +17350,7 @@
         </is>
       </c>
       <c r="E440" s="10" t="n">
-        <v>0.3102059610897492</v>
+        <v>-0.0389674951035675</v>
       </c>
       <c r="F440" s="10" t="n">
         <v>0.2390014</v>
@@ -17387,7 +17387,7 @@
         </is>
       </c>
       <c r="E441" s="6" t="n">
-        <v>0.1349512476476608</v>
+        <v>0.2270742663647302</v>
       </c>
       <c r="F441" s="6" t="n">
         <v>0.5758217</v>
@@ -17424,7 +17424,7 @@
         </is>
       </c>
       <c r="E442" s="10" t="n">
-        <v>-1.291082126500291</v>
+        <v>-0.9068884401666746</v>
       </c>
       <c r="F442" s="10" t="n">
         <v>0</v>
@@ -17461,7 +17461,7 @@
         </is>
       </c>
       <c r="E443" s="6" t="n">
-        <v>0.8084548672356971</v>
+        <v>0.5339093576001739</v>
       </c>
       <c r="F443" s="6" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
         </is>
       </c>
       <c r="E444" s="10" t="n">
-        <v>-0.3733870956307621</v>
+        <v>-0.5104865532265027</v>
       </c>
       <c r="F444" s="10" t="n">
         <v>0</v>
@@ -17535,7 +17535,7 @@
         </is>
       </c>
       <c r="E445" s="6" t="n">
-        <v>-0.0462580309312802</v>
+        <v>-0.053401841650276</v>
       </c>
       <c r="F445" s="6" t="n">
         <v>0.15447381</v>
@@ -17572,7 +17572,7 @@
         </is>
       </c>
       <c r="E446" s="10" t="n">
-        <v>0.5060977217365368</v>
+        <v>0.3171485441323036</v>
       </c>
       <c r="F446" s="10" t="n">
         <v>0.07660727000000001</v>
@@ -17609,7 +17609,7 @@
         </is>
       </c>
       <c r="E447" s="6" t="n">
-        <v>1.115781306739532</v>
+        <v>0.9079884059013964</v>
       </c>
       <c r="F447" s="6" t="n">
         <v>0.7902439999999999</v>
@@ -17646,7 +17646,7 @@
         </is>
       </c>
       <c r="E448" s="10" t="n">
-        <v>0.5671616950238551</v>
+        <v>0.1141420695281751</v>
       </c>
       <c r="F448" s="10" t="n">
         <v>0</v>
@@ -17683,7 +17683,7 @@
         </is>
       </c>
       <c r="E449" s="6" t="n">
-        <v>0.7818007622968665</v>
+        <v>1.570986181132604</v>
       </c>
       <c r="F449" s="6" t="n">
         <v>0.09184958</v>
@@ -17720,7 +17720,7 @@
         </is>
       </c>
       <c r="E450" s="10" t="n">
-        <v>0.1077529509663249</v>
+        <v>-0.9480821534235614</v>
       </c>
       <c r="F450" s="10" t="n">
         <v>0.076021045</v>
@@ -17757,7 +17757,7 @@
         </is>
       </c>
       <c r="E451" s="6" t="n">
-        <v>-1.399711365665513</v>
+        <v>-0.6888299144879745</v>
       </c>
       <c r="F451" s="6" t="n">
         <v>0</v>
@@ -17794,7 +17794,7 @@
         </is>
       </c>
       <c r="E452" s="10" t="n">
-        <v>0.3585691382262754</v>
+        <v>1.131916884796367</v>
       </c>
       <c r="F452" s="10" t="n">
         <v>0</v>
@@ -17831,7 +17831,7 @@
         </is>
       </c>
       <c r="E453" s="6" t="n">
-        <v>-0.2275536108070901</v>
+        <v>0.1917742006085181</v>
       </c>
       <c r="F453" s="6" t="n">
         <v>0.6192365</v>
@@ -17868,7 +17868,7 @@
         </is>
       </c>
       <c r="E454" s="10" t="n">
-        <v>-0.7786873573388036</v>
+        <v>-1.184462351859906</v>
       </c>
       <c r="F454" s="10" t="n">
         <v>0.2206438</v>
@@ -17905,7 +17905,7 @@
         </is>
       </c>
       <c r="E455" s="6" t="n">
-        <v>-0.8580750819020947</v>
+        <v>-0.8164734643663153</v>
       </c>
       <c r="F455" s="6" t="n">
         <v>0</v>
@@ -17942,7 +17942,7 @@
         </is>
       </c>
       <c r="E456" s="10" t="n">
-        <v>-0.2763141534048161</v>
+        <v>-0.5503716895530152</v>
       </c>
       <c r="F456" s="10" t="n">
         <v>0</v>
@@ -17979,7 +17979,7 @@
         </is>
       </c>
       <c r="E457" s="6" t="n">
-        <v>-0.576177740626435</v>
+        <v>-0.6083275075788727</v>
       </c>
       <c r="F457" s="6" t="n">
         <v>0</v>
@@ -18016,7 +18016,7 @@
         </is>
       </c>
       <c r="E458" s="10" t="n">
-        <v>0.2188832537972939</v>
+        <v>0.3168551685456603</v>
       </c>
       <c r="F458" s="10" t="n">
         <v>0</v>
@@ -18053,7 +18053,7 @@
         </is>
       </c>
       <c r="E459" s="6" t="n">
-        <v>0.5667634418277133</v>
+        <v>0.8962770685757079</v>
       </c>
       <c r="F459" s="6" t="n">
         <v>0.3904686</v>
@@ -18090,7 +18090,7 @@
         </is>
       </c>
       <c r="E460" s="10" t="n">
-        <v>0.3777957443165705</v>
+        <v>0.4936878677686732</v>
       </c>
       <c r="F460" s="10" t="n">
         <v>0</v>
@@ -18127,7 +18127,7 @@
         </is>
       </c>
       <c r="E461" s="6" t="n">
-        <v>1.045721379257582</v>
+        <v>0.8923154519304685</v>
       </c>
       <c r="F461" s="6" t="n">
         <v>0</v>
@@ -18164,7 +18164,7 @@
         </is>
       </c>
       <c r="E462" s="10" t="n">
-        <v>-1.44710579807512</v>
+        <v>-0.3990960578293259</v>
       </c>
       <c r="F462" s="10" t="n">
         <v>0</v>
@@ -18201,7 +18201,7 @@
         </is>
       </c>
       <c r="E463" s="6" t="n">
-        <v>-0.0874734394245026</v>
+        <v>0.9012164530512714</v>
       </c>
       <c r="F463" s="6" t="n">
         <v>0</v>
@@ -18238,7 +18238,7 @@
         </is>
       </c>
       <c r="E464" s="10" t="n">
-        <v>0.1342288252284679</v>
+        <v>1.102851283577598</v>
       </c>
       <c r="F464" s="10" t="n">
         <v>0.1622435</v>
@@ -18275,7 +18275,7 @@
         </is>
       </c>
       <c r="E465" s="6" t="n">
-        <v>-0.4487391497944843</v>
+        <v>-0.9943010267982832</v>
       </c>
       <c r="F465" s="6" t="n">
         <v>0.590367</v>
@@ -18312,7 +18312,7 @@
         </is>
       </c>
       <c r="E466" s="10" t="n">
-        <v>0.5722708712949652</v>
+        <v>0.6550958368005143</v>
       </c>
       <c r="F466" s="10" t="n">
         <v>0.32472655</v>
@@ -18349,7 +18349,7 @@
         </is>
       </c>
       <c r="E467" s="6" t="n">
-        <v>0.2168042086521149</v>
+        <v>0.2885090426058785</v>
       </c>
       <c r="F467" s="6" t="n">
         <v>0.1349818</v>
@@ -18386,7 +18386,7 @@
         </is>
       </c>
       <c r="E468" s="10" t="n">
-        <v>-0.2247690291657633</v>
+        <v>0.1185789626245456</v>
       </c>
       <c r="F468" s="10" t="n">
         <v>0</v>
@@ -18423,7 +18423,7 @@
         </is>
       </c>
       <c r="E469" s="6" t="n">
-        <v>0.2020965651786591</v>
+        <v>0.2008028834809358</v>
       </c>
       <c r="F469" s="6" t="n">
         <v>0.1671543</v>
@@ -18460,7 +18460,7 @@
         </is>
       </c>
       <c r="E470" s="10" t="n">
-        <v>-0.4946614736201177</v>
+        <v>-0.2103391313953327</v>
       </c>
       <c r="F470" s="10" t="n">
         <v>0</v>
@@ -18497,7 +18497,7 @@
         </is>
       </c>
       <c r="E471" s="6" t="n">
-        <v>0.440955386970874</v>
+        <v>0.4094327003996152</v>
       </c>
       <c r="F471" s="6" t="n">
         <v>0.09571130999999999</v>
@@ -18534,7 +18534,7 @@
         </is>
       </c>
       <c r="E472" s="10" t="n">
-        <v>-0.8092235118204369</v>
+        <v>-0.5023089712185237</v>
       </c>
       <c r="F472" s="10" t="n">
         <v>0.15166451</v>
@@ -18571,7 +18571,7 @@
         </is>
       </c>
       <c r="E473" s="6" t="n">
-        <v>0.5547664568019325</v>
+        <v>0.6239210018945286</v>
       </c>
       <c r="F473" s="6" t="n">
         <v>0.37060976</v>
@@ -18608,7 +18608,7 @@
         </is>
       </c>
       <c r="E474" s="10" t="n">
-        <v>1.157239061973226</v>
+        <v>0.4170212675777688</v>
       </c>
       <c r="F474" s="10" t="n">
         <v>0.44168845</v>
@@ -18645,7 +18645,7 @@
         </is>
       </c>
       <c r="E475" s="6" t="n">
-        <v>0.7137518271350941</v>
+        <v>0.3015782623863456</v>
       </c>
       <c r="F475" s="6" t="n">
         <v>0</v>
@@ -18682,7 +18682,7 @@
         </is>
       </c>
       <c r="E476" s="10" t="n">
-        <v>0.5369885865698322</v>
+        <v>-0.1069380251577933</v>
       </c>
       <c r="F476" s="10" t="n">
         <v>0</v>
@@ -18719,7 +18719,7 @@
         </is>
       </c>
       <c r="E477" s="6" t="n">
-        <v>-0.4645223614380078</v>
+        <v>-0.4611545701519834</v>
       </c>
       <c r="F477" s="6" t="n">
         <v>0.10292592</v>
@@ -18756,7 +18756,7 @@
         </is>
       </c>
       <c r="E478" s="10" t="n">
-        <v>0.2088448515965378</v>
+        <v>-0.2357550573773148</v>
       </c>
       <c r="F478" s="10" t="n">
         <v>0.63488483</v>
@@ -18793,7 +18793,7 @@
         </is>
       </c>
       <c r="E479" s="6" t="n">
-        <v>0.4671634834868969</v>
+        <v>0.127520017678237</v>
       </c>
       <c r="F479" s="6" t="n">
         <v>0.18232484</v>
@@ -18830,7 +18830,7 @@
         </is>
       </c>
       <c r="E480" s="10" t="n">
-        <v>-0.5472498828852438</v>
+        <v>-0.8591869358638472</v>
       </c>
       <c r="F480" s="10" t="n">
         <v>0</v>
@@ -18867,7 +18867,7 @@
         </is>
       </c>
       <c r="E481" s="6" t="n">
-        <v>0.0831870561864473</v>
+        <v>1.346727939942465</v>
       </c>
       <c r="F481" s="6" t="n">
         <v>0.194248</v>
@@ -18904,7 +18904,7 @@
         </is>
       </c>
       <c r="E482" s="10" t="n">
-        <v>1.430233100185343</v>
+        <v>1.652147010653488</v>
       </c>
       <c r="F482" s="10" t="n">
         <v>0</v>
@@ -18941,7 +18941,7 @@
         </is>
       </c>
       <c r="E483" s="6" t="n">
-        <v>0.8499150338619236</v>
+        <v>0.5601294413444364</v>
       </c>
       <c r="F483" s="6" t="n">
         <v>0</v>
@@ -18978,7 +18978,7 @@
         </is>
       </c>
       <c r="E484" s="10" t="n">
-        <v>1.073375766404717</v>
+        <v>0.9832092245134316</v>
       </c>
       <c r="F484" s="10" t="n">
         <v>0</v>
@@ -19015,7 +19015,7 @@
         </is>
       </c>
       <c r="E485" s="6" t="n">
-        <v>0.8146176724671506</v>
+        <v>1.098730807648337</v>
       </c>
       <c r="F485" s="6" t="n">
         <v>0.11216543</v>
@@ -19052,7 +19052,7 @@
         </is>
       </c>
       <c r="E486" s="10" t="n">
-        <v>-0.8818427559370292</v>
+        <v>-0.7948390678783527</v>
       </c>
       <c r="F486" s="10" t="n">
         <v>0.2702092</v>
@@ -19089,7 +19089,7 @@
         </is>
       </c>
       <c r="E487" s="6" t="n">
-        <v>0.5065739802146162</v>
+        <v>1.710087347893074</v>
       </c>
       <c r="F487" s="6" t="n">
         <v>0</v>
@@ -19126,7 +19126,7 @@
         </is>
       </c>
       <c r="E488" s="10" t="n">
-        <v>0.7630386746402985</v>
+        <v>1.162991964124905</v>
       </c>
       <c r="F488" s="10" t="n">
         <v>0.10574664</v>
@@ -19163,7 +19163,7 @@
         </is>
       </c>
       <c r="E489" s="6" t="n">
-        <v>0.8438638616918066</v>
+        <v>-0.3334932169330561</v>
       </c>
       <c r="F489" s="6" t="n">
         <v>0</v>
@@ -19200,7 +19200,7 @@
         </is>
       </c>
       <c r="E490" s="10" t="n">
-        <v>-0.4145025642489894</v>
+        <v>-0.6307987485990297</v>
       </c>
       <c r="F490" s="10" t="n">
         <v>0.35464564</v>
@@ -19237,7 +19237,7 @@
         </is>
       </c>
       <c r="E491" s="6" t="n">
-        <v>-0.4880671814244281</v>
+        <v>-0.3059124344666629</v>
       </c>
       <c r="F491" s="6" t="n">
         <v>0.66671264</v>
@@ -19274,7 +19274,7 @@
         </is>
       </c>
       <c r="E492" s="10" t="n">
-        <v>-1.114174739480375</v>
+        <v>-0.5770707847407827</v>
       </c>
       <c r="F492" s="10" t="n">
         <v>0</v>
@@ -19311,7 +19311,7 @@
         </is>
       </c>
       <c r="E493" s="6" t="n">
-        <v>0.4830021797221717</v>
+        <v>-0.5178417480196938</v>
       </c>
       <c r="F493" s="6" t="n">
         <v>0.8176666</v>
@@ -19348,7 +19348,7 @@
         </is>
       </c>
       <c r="E494" s="10" t="n">
-        <v>-0.8457102235636212</v>
+        <v>-0.7765165386650262</v>
       </c>
       <c r="F494" s="10" t="n">
         <v>0</v>
@@ -19385,7 +19385,7 @@
         </is>
       </c>
       <c r="E495" s="6" t="n">
-        <v>0.7311255734604751</v>
+        <v>0.7386778356574797</v>
       </c>
       <c r="F495" s="6" t="n">
         <v>0.42275268</v>
@@ -19422,7 +19422,7 @@
         </is>
       </c>
       <c r="E496" s="10" t="n">
-        <v>-0.8822103185150779</v>
+        <v>-0.8460732686503715</v>
       </c>
       <c r="F496" s="10" t="n">
         <v>0</v>
@@ -19459,7 +19459,7 @@
         </is>
       </c>
       <c r="E497" s="6" t="n">
-        <v>0.4750704426028121</v>
+        <v>0.1483170295997757</v>
       </c>
       <c r="F497" s="6" t="n">
         <v>0.09644446</v>
@@ -19496,7 +19496,7 @@
         </is>
       </c>
       <c r="E498" s="10" t="n">
-        <v>0.6924885198928624</v>
+        <v>-0.1556724441426296</v>
       </c>
       <c r="F498" s="10" t="n">
         <v>0</v>
@@ -19533,7 +19533,7 @@
         </is>
       </c>
       <c r="E499" s="6" t="n">
-        <v>-0.2089691430781758</v>
+        <v>0.3429387227970137</v>
       </c>
       <c r="F499" s="6" t="n">
         <v>0</v>
@@ -19570,7 +19570,7 @@
         </is>
       </c>
       <c r="E500" s="10" t="n">
-        <v>0.2503940068591727</v>
+        <v>-0.08996601756871241</v>
       </c>
       <c r="F500" s="10" t="n">
         <v>0.6077151</v>
@@ -19607,7 +19607,7 @@
         </is>
       </c>
       <c r="E501" s="6" t="n">
-        <v>1.092700744324225</v>
+        <v>-0.0229232592089923</v>
       </c>
       <c r="F501" s="6" t="n">
         <v>0.79023564</v>
@@ -19644,7 +19644,7 @@
         </is>
       </c>
       <c r="E502" s="10" t="n">
-        <v>1.100466450641478</v>
+        <v>-0.1052638870519867</v>
       </c>
       <c r="F502" s="10" t="n">
         <v>0.7764791</v>
@@ -19681,7 +19681,7 @@
         </is>
       </c>
       <c r="E503" s="6" t="n">
-        <v>0.1149093455655255</v>
+        <v>0.6369897611634339</v>
       </c>
       <c r="F503" s="6" t="n">
         <v>0.61865264</v>
@@ -19718,7 +19718,7 @@
         </is>
       </c>
       <c r="E504" s="10" t="n">
-        <v>0.0895401555498532</v>
+        <v>-0.3599381292698538</v>
       </c>
       <c r="F504" s="10" t="n">
         <v>0.56012726</v>
@@ -19755,7 +19755,7 @@
         </is>
       </c>
       <c r="E505" s="6" t="n">
-        <v>-0.0591976596399745</v>
+        <v>-0.314401065036103</v>
       </c>
       <c r="F505" s="6" t="n">
         <v>0.64674586</v>
@@ -19792,7 +19792,7 @@
         </is>
       </c>
       <c r="E506" s="10" t="n">
-        <v>1.242546153328646</v>
+        <v>1.066278767339318</v>
       </c>
       <c r="F506" s="10" t="n">
         <v>0</v>
@@ -19829,7 +19829,7 @@
         </is>
       </c>
       <c r="E507" s="6" t="n">
-        <v>1.850333863474237</v>
+        <v>2.482548272111246</v>
       </c>
       <c r="F507" s="6" t="n">
         <v>0</v>
@@ -19866,7 +19866,7 @@
         </is>
       </c>
       <c r="E508" s="10" t="n">
-        <v>0.3866191095561087</v>
+        <v>0.4466643188545616</v>
       </c>
       <c r="F508" s="10" t="n">
         <v>0.39466184</v>
@@ -19903,7 +19903,7 @@
         </is>
       </c>
       <c r="E509" s="6" t="n">
-        <v>0.618585506363824</v>
+        <v>1.270737614182155</v>
       </c>
       <c r="F509" s="6" t="n">
         <v>0</v>
@@ -19940,7 +19940,7 @@
         </is>
       </c>
       <c r="E510" s="10" t="n">
-        <v>0.1809944699467465</v>
+        <v>1.111522032024426</v>
       </c>
       <c r="F510" s="10" t="n">
         <v>0.5386566</v>
@@ -19977,7 +19977,7 @@
         </is>
       </c>
       <c r="E511" s="6" t="n">
-        <v>-0.3364706581756949</v>
+        <v>0.1650149115055324</v>
       </c>
       <c r="F511" s="6" t="n">
         <v>0.07109635</v>
@@ -20014,7 +20014,7 @@
         </is>
       </c>
       <c r="E512" s="10" t="n">
-        <v>-0.1987972825785855</v>
+        <v>-0.2786951570921704</v>
       </c>
       <c r="F512" s="10" t="n">
         <v>0</v>
@@ -20051,7 +20051,7 @@
         </is>
       </c>
       <c r="E513" s="6" t="n">
-        <v>-0.0019053517906747</v>
+        <v>0.217586625051729</v>
       </c>
       <c r="F513" s="6" t="n">
         <v>0</v>
@@ -20088,7 +20088,7 @@
         </is>
       </c>
       <c r="E514" s="10" t="n">
-        <v>-0.06468469960101481</v>
+        <v>-0.3384353257782291</v>
       </c>
       <c r="F514" s="10" t="n">
         <v>0.34793845</v>
@@ -20125,7 +20125,7 @@
         </is>
       </c>
       <c r="E515" s="6" t="n">
-        <v>-0.5762609068331218</v>
+        <v>-0.2127998202305924</v>
       </c>
       <c r="F515" s="6" t="n">
         <v>0</v>
@@ -20162,7 +20162,7 @@
         </is>
       </c>
       <c r="E516" s="10" t="n">
-        <v>1.679434396562403</v>
+        <v>1.571772752592654</v>
       </c>
       <c r="F516" s="10" t="n">
         <v>0</v>
@@ -20199,7 +20199,7 @@
         </is>
       </c>
       <c r="E517" s="6" t="n">
-        <v>-0.1069349746774768</v>
+        <v>0.0294526789183903</v>
       </c>
       <c r="F517" s="6" t="n">
         <v>0.64549553</v>
@@ -20236,7 +20236,7 @@
         </is>
       </c>
       <c r="E518" s="10" t="n">
-        <v>-0.1006780893937882</v>
+        <v>0.599624943035688</v>
       </c>
       <c r="F518" s="10" t="n">
         <v>0</v>
@@ -20273,7 +20273,7 @@
         </is>
       </c>
       <c r="E519" s="6" t="n">
-        <v>-0.8772806954427165</v>
+        <v>-0.4958168352537499</v>
       </c>
       <c r="F519" s="6" t="n">
         <v>0</v>
@@ -20310,7 +20310,7 @@
         </is>
       </c>
       <c r="E520" s="10" t="n">
-        <v>-0.123975435514152</v>
+        <v>0.6611323498831267</v>
       </c>
       <c r="F520" s="10" t="n">
         <v>0.2973354</v>
@@ -20347,7 +20347,7 @@
         </is>
       </c>
       <c r="E521" s="6" t="n">
-        <v>-0.7017365039833532</v>
+        <v>-0.5370173517162639</v>
       </c>
       <c r="F521" s="6" t="n">
         <v>0</v>
@@ -20384,7 +20384,7 @@
         </is>
       </c>
       <c r="E522" s="10" t="n">
-        <v>-0.2045963167212158</v>
+        <v>0.1113159329218144</v>
       </c>
       <c r="F522" s="10" t="n">
         <v>0</v>
@@ -20421,7 +20421,7 @@
         </is>
       </c>
       <c r="E523" s="6" t="n">
-        <v>-0.3529980046740281</v>
+        <v>-0.3039120957362464</v>
       </c>
       <c r="F523" s="6" t="n">
         <v>0</v>
@@ -20458,7 +20458,7 @@
         </is>
       </c>
       <c r="E524" s="10" t="n">
-        <v>-0.4423253165446864</v>
+        <v>-0.1305302201684009</v>
       </c>
       <c r="F524" s="10" t="n">
         <v>0.14350851</v>
@@ -20495,7 +20495,7 @@
         </is>
       </c>
       <c r="E525" s="6" t="n">
-        <v>-1.385238948451077</v>
+        <v>-0.5358183311687786</v>
       </c>
       <c r="F525" s="6" t="n">
         <v>0.7616713000000001</v>
@@ -20532,7 +20532,7 @@
         </is>
       </c>
       <c r="E526" s="10" t="n">
-        <v>1.135915765889417</v>
+        <v>1.937564863373018</v>
       </c>
       <c r="F526" s="10" t="n">
         <v>0.38483593</v>
@@ -20569,7 +20569,7 @@
         </is>
       </c>
       <c r="E527" s="6" t="n">
-        <v>-1.065164671016349</v>
+        <v>-1.261126900454351</v>
       </c>
       <c r="F527" s="6" t="n">
         <v>0</v>
@@ -20606,7 +20606,7 @@
         </is>
       </c>
       <c r="E528" s="10" t="n">
-        <v>-0.07120167704365971</v>
+        <v>-0.1957894021774225</v>
       </c>
       <c r="F528" s="10" t="n">
         <v>0</v>
@@ -20643,7 +20643,7 @@
         </is>
       </c>
       <c r="E529" s="6" t="n">
-        <v>-0.1630078924358545</v>
+        <v>-0.3165163179657981</v>
       </c>
       <c r="F529" s="6" t="n">
         <v>0.1487804</v>
@@ -20680,7 +20680,7 @@
         </is>
       </c>
       <c r="E530" s="10" t="n">
-        <v>0.8740614303849957</v>
+        <v>1.188917875278326</v>
       </c>
       <c r="F530" s="10" t="n">
         <v>0</v>
@@ -20717,7 +20717,7 @@
         </is>
       </c>
       <c r="E531" s="6" t="n">
-        <v>-0.0498257615089709</v>
+        <v>-0.4873075380787967</v>
       </c>
       <c r="F531" s="6" t="n">
         <v>0</v>
@@ -20754,7 +20754,7 @@
         </is>
       </c>
       <c r="E532" s="10" t="n">
-        <v>0.0957027870789688</v>
+        <v>0.2742133007215194</v>
       </c>
       <c r="F532" s="10" t="n">
         <v>0.22161964</v>
@@ -20791,7 +20791,7 @@
         </is>
       </c>
       <c r="E533" s="6" t="n">
-        <v>0.4817854429037682</v>
+        <v>0.1729344403901053</v>
       </c>
       <c r="F533" s="6" t="n">
         <v>0</v>
@@ -20828,7 +20828,7 @@
         </is>
       </c>
       <c r="E534" s="10" t="n">
-        <v>-0.2150489965528441</v>
+        <v>0.1239687370024973</v>
       </c>
       <c r="F534" s="10" t="n">
         <v>0</v>
@@ -20865,7 +20865,7 @@
         </is>
       </c>
       <c r="E535" s="6" t="n">
-        <v>-0.4623413410073502</v>
+        <v>-1.084891159503421</v>
       </c>
       <c r="F535" s="6" t="n">
         <v>0.26267123</v>
@@ -20902,7 +20902,7 @@
         </is>
       </c>
       <c r="E536" s="10" t="n">
-        <v>-0.7485636235346401</v>
+        <v>-1.148094721675645</v>
       </c>
       <c r="F536" s="10" t="n">
         <v>0.3344932</v>
@@ -20939,7 +20939,7 @@
         </is>
       </c>
       <c r="E537" s="6" t="n">
-        <v>-1.347189374051301</v>
+        <v>-1.12827342771781</v>
       </c>
       <c r="F537" s="6" t="n">
         <v>0.66484195</v>
@@ -20976,7 +20976,7 @@
         </is>
       </c>
       <c r="E538" s="10" t="n">
-        <v>0.3756784605961008</v>
+        <v>0.6618585635252058</v>
       </c>
       <c r="F538" s="10" t="n">
         <v>0.26035383</v>
@@ -21013,7 +21013,7 @@
         </is>
       </c>
       <c r="E539" s="6" t="n">
-        <v>-0.2475566265484188</v>
+        <v>0.4465901034521827</v>
       </c>
       <c r="F539" s="6" t="n">
         <v>0.16159333</v>
@@ -21050,7 +21050,7 @@
         </is>
       </c>
       <c r="E540" s="10" t="n">
-        <v>0.1161567898516807</v>
+        <v>0.2311445611228368</v>
       </c>
       <c r="F540" s="10" t="n">
         <v>0.7550575</v>
@@ -21087,7 +21087,7 @@
         </is>
       </c>
       <c r="E541" s="6" t="n">
-        <v>0.1077685771505467</v>
+        <v>-0.1624165419357432</v>
       </c>
       <c r="F541" s="6" t="n">
         <v>0</v>
@@ -21124,7 +21124,7 @@
         </is>
       </c>
       <c r="E542" s="10" t="n">
-        <v>0.1784372285455678</v>
+        <v>0.6373940442573908</v>
       </c>
       <c r="F542" s="10" t="n">
         <v>0.74221814</v>
@@ -21161,7 +21161,7 @@
         </is>
       </c>
       <c r="E543" s="6" t="n">
-        <v>0.7816051962961689</v>
+        <v>0.0002673051392518</v>
       </c>
       <c r="F543" s="6" t="n">
         <v>0.5969152</v>
@@ -21198,7 +21198,7 @@
         </is>
       </c>
       <c r="E544" s="10" t="n">
-        <v>0.4153394069903329</v>
+        <v>-0.0233444154415785</v>
       </c>
       <c r="F544" s="10" t="n">
         <v>0</v>
@@ -21235,7 +21235,7 @@
         </is>
       </c>
       <c r="E545" s="6" t="n">
-        <v>-0.3276306715526723</v>
+        <v>0.7483496331864049</v>
       </c>
       <c r="F545" s="6" t="n">
         <v>0</v>
@@ -21272,7 +21272,7 @@
         </is>
       </c>
       <c r="E546" s="10" t="n">
-        <v>-0.769903895227928</v>
+        <v>0.0024717797075682</v>
       </c>
       <c r="F546" s="10" t="n">
         <v>0</v>
@@ -21309,7 +21309,7 @@
         </is>
       </c>
       <c r="E547" s="6" t="n">
-        <v>-0.6581960034929711</v>
+        <v>-0.1449600326844411</v>
       </c>
       <c r="F547" s="6" t="n">
         <v>0.14303711</v>
@@ -21346,7 +21346,7 @@
         </is>
       </c>
       <c r="E548" s="10" t="n">
-        <v>0.766099168796468</v>
+        <v>1.126965705902313</v>
       </c>
       <c r="F548" s="10" t="n">
         <v>0</v>
@@ -21383,7 +21383,7 @@
         </is>
       </c>
       <c r="E549" s="6" t="n">
-        <v>0.8663472565451856</v>
+        <v>0.6696154683103757</v>
       </c>
       <c r="F549" s="6" t="n">
         <v>0.83300143</v>
@@ -21420,7 +21420,7 @@
         </is>
       </c>
       <c r="E550" s="10" t="n">
-        <v>1.372665057905714</v>
+        <v>1.104022089697676</v>
       </c>
       <c r="F550" s="10" t="n">
         <v>0.6715456</v>
@@ -21457,7 +21457,7 @@
         </is>
       </c>
       <c r="E551" s="6" t="n">
-        <v>-1.107071425340859</v>
+        <v>-0.2881236147691355</v>
       </c>
       <c r="F551" s="6" t="n">
         <v>0</v>
@@ -21494,7 +21494,7 @@
         </is>
       </c>
       <c r="E552" s="10" t="n">
-        <v>-0.0517571561041591</v>
+        <v>-0.5597520184285872</v>
       </c>
       <c r="F552" s="10" t="n">
         <v>0</v>
@@ -21531,7 +21531,7 @@
         </is>
       </c>
       <c r="E553" s="6" t="n">
-        <v>0.8337946549344716</v>
+        <v>0.584931484611546</v>
       </c>
       <c r="F553" s="6" t="n">
         <v>0.5248635</v>
@@ -21568,7 +21568,7 @@
         </is>
       </c>
       <c r="E554" s="10" t="n">
-        <v>-0.347963477304943</v>
+        <v>-0.0226225426548894</v>
       </c>
       <c r="F554" s="10" t="n">
         <v>0.1301168</v>
@@ -21605,7 +21605,7 @@
         </is>
       </c>
       <c r="E555" s="6" t="n">
-        <v>0.0498766037395294</v>
+        <v>0.6222104643618741</v>
       </c>
       <c r="F555" s="6" t="n">
         <v>0.6545676</v>
@@ -21642,7 +21642,7 @@
         </is>
       </c>
       <c r="E556" s="10" t="n">
-        <v>-0.1164549430682845</v>
+        <v>-0.2988184085743309</v>
       </c>
       <c r="F556" s="10" t="n">
         <v>0.36826771</v>
@@ -21679,7 +21679,7 @@
         </is>
       </c>
       <c r="E557" s="6" t="n">
-        <v>-0.4171183751822994</v>
+        <v>-0.6890107764000818</v>
       </c>
       <c r="F557" s="6" t="n">
         <v>0.08624153599999999</v>
@@ -21716,7 +21716,7 @@
         </is>
       </c>
       <c r="E558" s="10" t="n">
-        <v>0.4759815549464166</v>
+        <v>1.010396742230811</v>
       </c>
       <c r="F558" s="10" t="n">
         <v>0</v>
@@ -21753,7 +21753,7 @@
         </is>
       </c>
       <c r="E559" s="6" t="n">
-        <v>0.457884503222304</v>
+        <v>0.3826025568112921</v>
       </c>
       <c r="F559" s="6" t="n">
         <v>0.67183167</v>
@@ -21790,7 +21790,7 @@
         </is>
       </c>
       <c r="E560" s="10" t="n">
-        <v>0.0408961474118518</v>
+        <v>-0.8389566186896517</v>
       </c>
       <c r="F560" s="10" t="n">
         <v>0.3571468</v>
@@ -21827,7 +21827,7 @@
         </is>
       </c>
       <c r="E561" s="6" t="n">
-        <v>-0.2468143010983642</v>
+        <v>-0.4185276691990006</v>
       </c>
       <c r="F561" s="6" t="n">
         <v>0</v>
@@ -21864,7 +21864,7 @@
         </is>
       </c>
       <c r="E562" s="10" t="n">
-        <v>-0.5105541406642417</v>
+        <v>-0.8007226144954288</v>
       </c>
       <c r="F562" s="10" t="n">
         <v>0</v>
@@ -21901,7 +21901,7 @@
         </is>
       </c>
       <c r="E563" s="6" t="n">
-        <v>0.7286196649027827</v>
+        <v>1.058419680201658</v>
       </c>
       <c r="F563" s="6" t="n">
         <v>0</v>
@@ -21938,7 +21938,7 @@
         </is>
       </c>
       <c r="E564" s="10" t="n">
-        <v>-0.927883223578604</v>
+        <v>-0.8756129841056102</v>
       </c>
       <c r="F564" s="10" t="n">
         <v>0</v>
@@ -21975,7 +21975,7 @@
         </is>
       </c>
       <c r="E565" s="6" t="n">
-        <v>0.0575421063446975</v>
+        <v>-0.1817802837331101</v>
       </c>
       <c r="F565" s="6" t="n">
         <v>0.6239013</v>
@@ -22012,7 +22012,7 @@
         </is>
       </c>
       <c r="E566" s="10" t="n">
-        <v>0.4157725156110951</v>
+        <v>0.2448401136063275</v>
       </c>
       <c r="F566" s="10" t="n">
         <v>0.42347473</v>
@@ -22049,7 +22049,7 @@
         </is>
       </c>
       <c r="E567" s="6" t="n">
-        <v>-0.3436099468163465</v>
+        <v>-0.2648383952225938</v>
       </c>
       <c r="F567" s="6" t="n">
         <v>0</v>
@@ -22086,7 +22086,7 @@
         </is>
       </c>
       <c r="E568" s="10" t="n">
-        <v>0.7595779327342473</v>
+        <v>0.5582125049745416</v>
       </c>
       <c r="F568" s="10" t="n">
         <v>0.25733903</v>
@@ -22123,7 +22123,7 @@
         </is>
       </c>
       <c r="E569" s="6" t="n">
-        <v>-0.2879188071499115</v>
+        <v>-0.9265899265650336</v>
       </c>
       <c r="F569" s="6" t="n">
         <v>0.6743954</v>
@@ -22160,7 +22160,7 @@
         </is>
       </c>
       <c r="E570" s="10" t="n">
-        <v>-0.5750086634054449</v>
+        <v>-0.3951694538807673</v>
       </c>
       <c r="F570" s="10" t="n">
         <v>0.2610404</v>
@@ -22197,7 +22197,7 @@
         </is>
       </c>
       <c r="E571" s="6" t="n">
-        <v>-0.0710852328114959</v>
+        <v>-0.6514444877233233</v>
       </c>
       <c r="F571" s="6" t="n">
         <v>0.7296317</v>
@@ -22234,7 +22234,7 @@
         </is>
       </c>
       <c r="E572" s="10" t="n">
-        <v>-0.371383377907</v>
+        <v>-0.3499223868399783</v>
       </c>
       <c r="F572" s="10" t="n">
         <v>0.09613644</v>
@@ -22271,7 +22271,7 @@
         </is>
       </c>
       <c r="E573" s="6" t="n">
-        <v>0.3484805272887988</v>
+        <v>0.2067542384443255</v>
       </c>
       <c r="F573" s="6" t="n">
         <v>0</v>
@@ -22308,7 +22308,7 @@
         </is>
       </c>
       <c r="E574" s="10" t="n">
-        <v>-0.310004842929524</v>
+        <v>-0.0499834417729205</v>
       </c>
       <c r="F574" s="10" t="n">
         <v>0.38626775</v>
@@ -22345,7 +22345,7 @@
         </is>
       </c>
       <c r="E575" s="6" t="n">
-        <v>0.0389944053176613</v>
+        <v>-0.3647306643929484</v>
       </c>
       <c r="F575" s="6" t="n">
         <v>0.3963209</v>
@@ -22382,7 +22382,7 @@
         </is>
       </c>
       <c r="E576" s="10" t="n">
-        <v>0.2935254623450834</v>
+        <v>-0.0556967472218134</v>
       </c>
       <c r="F576" s="10" t="n">
         <v>0</v>
@@ -22419,7 +22419,7 @@
         </is>
       </c>
       <c r="E577" s="6" t="n">
-        <v>-0.1799545990724894</v>
+        <v>-0.764091860582475</v>
       </c>
       <c r="F577" s="6" t="n">
         <v>0.16288273</v>
@@ -22456,7 +22456,7 @@
         </is>
       </c>
       <c r="E578" s="10" t="n">
-        <v>-0.0338377257260577</v>
+        <v>0.7271316487792658</v>
       </c>
       <c r="F578" s="10" t="n">
         <v>0.6285944999999999</v>
@@ -22493,7 +22493,7 @@
         </is>
       </c>
       <c r="E579" s="6" t="n">
-        <v>-0.1457678399624713</v>
+        <v>-0.8622591630310247</v>
       </c>
       <c r="F579" s="6" t="n">
         <v>0</v>
@@ -22530,7 +22530,7 @@
         </is>
       </c>
       <c r="E580" s="10" t="n">
-        <v>-0.585735374444914</v>
+        <v>-0.7347682118052057</v>
       </c>
       <c r="F580" s="10" t="n">
         <v>0</v>
@@ -22567,7 +22567,7 @@
         </is>
       </c>
       <c r="E581" s="6" t="n">
-        <v>-0.3277784472082946</v>
+        <v>0.2816826107623753</v>
       </c>
       <c r="F581" s="6" t="n">
         <v>0</v>
@@ -22604,7 +22604,7 @@
         </is>
       </c>
       <c r="E582" s="10" t="n">
-        <v>0.2720388510425555</v>
+        <v>-0.4790122399164946</v>
       </c>
       <c r="F582" s="10" t="n">
         <v>0</v>
@@ -22641,7 +22641,7 @@
         </is>
       </c>
       <c r="E583" s="6" t="n">
-        <v>0.3863769011218361</v>
+        <v>0.2037166170583656</v>
       </c>
       <c r="F583" s="6" t="n">
         <v>0</v>
@@ -22678,7 +22678,7 @@
         </is>
       </c>
       <c r="E584" s="10" t="n">
-        <v>0.265340720744113</v>
+        <v>-0.1600336623454626</v>
       </c>
       <c r="F584" s="10" t="n">
         <v>0.20198174</v>
@@ -22715,7 +22715,7 @@
         </is>
       </c>
       <c r="E585" s="6" t="n">
-        <v>-0.1670305610839532</v>
+        <v>0.8068145196397868</v>
       </c>
       <c r="F585" s="6" t="n">
         <v>0</v>
@@ -22752,7 +22752,7 @@
         </is>
       </c>
       <c r="E586" s="10" t="n">
-        <v>-1.150551936690444</v>
+        <v>-0.4623113105919554</v>
       </c>
       <c r="F586" s="10" t="n">
         <v>0</v>
@@ -22789,7 +22789,7 @@
         </is>
       </c>
       <c r="E587" s="6" t="n">
-        <v>-0.8463117866561364</v>
+        <v>-0.3692399141379738</v>
       </c>
       <c r="F587" s="6" t="n">
         <v>0</v>
@@ -22826,7 +22826,7 @@
         </is>
       </c>
       <c r="E588" s="10" t="n">
-        <v>-0.776344875834305</v>
+        <v>-0.3021651477784344</v>
       </c>
       <c r="F588" s="10" t="n">
         <v>0</v>
@@ -22863,7 +22863,7 @@
         </is>
       </c>
       <c r="E589" s="6" t="n">
-        <v>-0.8985967505872058</v>
+        <v>-0.7484960819532177</v>
       </c>
       <c r="F589" s="6" t="n">
         <v>0.15712284</v>
@@ -22900,7 +22900,7 @@
         </is>
       </c>
       <c r="E590" s="10" t="n">
-        <v>-0.1750307438987198</v>
+        <v>-1.611564327119598</v>
       </c>
       <c r="F590" s="10" t="n">
         <v>0.32332852</v>
@@ -22937,7 +22937,7 @@
         </is>
       </c>
       <c r="E591" s="6" t="n">
-        <v>0.27846607266314</v>
+        <v>-0.0198233161555962</v>
       </c>
       <c r="F591" s="6" t="n">
         <v>0</v>
@@ -22974,7 +22974,7 @@
         </is>
       </c>
       <c r="E592" s="10" t="n">
-        <v>-0.5765554781164622</v>
+        <v>-1.054638913635373</v>
       </c>
       <c r="F592" s="10" t="n">
         <v>0.117978744</v>
@@ -23011,7 +23011,7 @@
         </is>
       </c>
       <c r="E593" s="6" t="n">
-        <v>-0.1654589244729549</v>
+        <v>-0.4307178525886832</v>
       </c>
       <c r="F593" s="6" t="n">
         <v>0.60309976</v>
@@ -23048,7 +23048,7 @@
         </is>
       </c>
       <c r="E594" s="10" t="n">
-        <v>-0.485380622819624</v>
+        <v>-0.6857599082421855</v>
       </c>
       <c r="F594" s="10" t="n">
         <v>0</v>
@@ -23085,7 +23085,7 @@
         </is>
       </c>
       <c r="E595" s="6" t="n">
-        <v>-0.8493371801476456</v>
+        <v>-0.6350481299574994</v>
       </c>
       <c r="F595" s="6" t="n">
         <v>0</v>
@@ -23122,7 +23122,7 @@
         </is>
       </c>
       <c r="E596" s="10" t="n">
-        <v>0.9878837623443903</v>
+        <v>0.5839708956975229</v>
       </c>
       <c r="F596" s="10" t="n">
         <v>0.4234085</v>
@@ -23159,7 +23159,7 @@
         </is>
       </c>
       <c r="E597" s="6" t="n">
-        <v>-0.8285359125372297</v>
+        <v>-1.009109910725703</v>
       </c>
       <c r="F597" s="6" t="n">
         <v>0</v>
@@ -23196,7 +23196,7 @@
         </is>
       </c>
       <c r="E598" s="10" t="n">
-        <v>-1.191537889058139</v>
+        <v>-1.095762063011792</v>
       </c>
       <c r="F598" s="10" t="n">
         <v>0.39502504</v>
@@ -23233,7 +23233,7 @@
         </is>
       </c>
       <c r="E599" s="6" t="n">
-        <v>0.0811097874952928</v>
+        <v>-0.7047029278861091</v>
       </c>
       <c r="F599" s="6" t="n">
         <v>0.25475633</v>
@@ -23270,7 +23270,7 @@
         </is>
       </c>
       <c r="E600" s="10" t="n">
-        <v>-0.870044140706785</v>
+        <v>-0.3484046771095106</v>
       </c>
       <c r="F600" s="10" t="n">
         <v>0</v>
@@ -23307,7 +23307,7 @@
         </is>
       </c>
       <c r="E601" s="6" t="n">
-        <v>-0.6015397068290899</v>
+        <v>-0.5517101442432001</v>
       </c>
       <c r="F601" s="6" t="n">
         <v>0.5077922</v>
@@ -23344,7 +23344,7 @@
         </is>
       </c>
       <c r="E602" s="10" t="n">
-        <v>-0.5284597293795161</v>
+        <v>-0.1485143056324908</v>
       </c>
       <c r="F602" s="10" t="n">
         <v>0.10042049</v>
@@ -23381,7 +23381,7 @@
         </is>
       </c>
       <c r="E603" s="6" t="n">
-        <v>0.1768853775033973</v>
+        <v>-0.2233295690912788</v>
       </c>
       <c r="F603" s="6" t="n">
         <v>0</v>
@@ -23418,7 +23418,7 @@
         </is>
       </c>
       <c r="E604" s="10" t="n">
-        <v>-0.1677692324907854</v>
+        <v>-0.086741824783162</v>
       </c>
       <c r="F604" s="10" t="n">
         <v>0.47452888</v>
@@ -23455,7 +23455,7 @@
         </is>
       </c>
       <c r="E605" s="6" t="n">
-        <v>-1.070651467566591</v>
+        <v>-0.6741674646851661</v>
       </c>
       <c r="F605" s="6" t="n">
         <v>0</v>
@@ -23492,7 +23492,7 @@
         </is>
       </c>
       <c r="E606" s="10" t="n">
-        <v>0.1892479755662609</v>
+        <v>-0.868554996332767</v>
       </c>
       <c r="F606" s="10" t="n">
         <v>0.47736397</v>
@@ -23529,7 +23529,7 @@
         </is>
       </c>
       <c r="E607" s="6" t="n">
-        <v>-0.3537913924343518</v>
+        <v>-0.1167612398099852</v>
       </c>
       <c r="F607" s="6" t="n">
         <v>0</v>
@@ -23566,7 +23566,7 @@
         </is>
       </c>
       <c r="E608" s="10" t="n">
-        <v>0.0677636972943285</v>
+        <v>-0.0166791467310453</v>
       </c>
       <c r="F608" s="10" t="n">
         <v>0</v>
@@ -23603,7 +23603,7 @@
         </is>
       </c>
       <c r="E609" s="6" t="n">
-        <v>0.1629722447999683</v>
+        <v>0.3320216375126152</v>
       </c>
       <c r="F609" s="6" t="n">
         <v>0.5494992</v>
@@ -23640,7 +23640,7 @@
         </is>
       </c>
       <c r="E610" s="10" t="n">
-        <v>0.2541700236588224</v>
+        <v>0.3563182863892837</v>
       </c>
       <c r="F610" s="10" t="n">
         <v>0</v>
@@ -23677,7 +23677,7 @@
         </is>
       </c>
       <c r="E611" s="6" t="n">
-        <v>-0.7117021514207393</v>
+        <v>-1.373305068444187</v>
       </c>
       <c r="F611" s="6" t="n">
         <v>0</v>
@@ -23714,7 +23714,7 @@
         </is>
       </c>
       <c r="E612" s="10" t="n">
-        <v>-0.4741846239115519</v>
+        <v>-0.1823197522813204</v>
       </c>
       <c r="F612" s="10" t="n">
         <v>0</v>
@@ -23751,7 +23751,7 @@
         </is>
       </c>
       <c r="E613" s="6" t="n">
-        <v>-0.3537939517133354</v>
+        <v>-0.1222986569178807</v>
       </c>
       <c r="F613" s="6" t="n">
         <v>0.64012873</v>
@@ -23788,7 +23788,7 @@
         </is>
       </c>
       <c r="E614" s="10" t="n">
-        <v>0.5722649950513682</v>
+        <v>-0.2392692880108363</v>
       </c>
       <c r="F614" s="10" t="n">
         <v>0</v>
@@ -23825,7 +23825,7 @@
         </is>
       </c>
       <c r="E615" s="6" t="n">
-        <v>1.623471735885909</v>
+        <v>1.366876137019833</v>
       </c>
       <c r="F615" s="6" t="n">
         <v>0.17189148</v>
@@ -23862,7 +23862,7 @@
         </is>
       </c>
       <c r="E616" s="10" t="n">
-        <v>-0.6589855941014187</v>
+        <v>-0.4743658644947433</v>
       </c>
       <c r="F616" s="10" t="n">
         <v>0.16339408</v>
@@ -23899,7 +23899,7 @@
         </is>
       </c>
       <c r="E617" s="6" t="n">
-        <v>0.1574400605858214</v>
+        <v>0.7737185624655515</v>
       </c>
       <c r="F617" s="6" t="n">
         <v>0.6423868</v>
@@ -23936,7 +23936,7 @@
         </is>
       </c>
       <c r="E618" s="10" t="n">
-        <v>0.6000423230195077</v>
+        <v>0.6289215782793321</v>
       </c>
       <c r="F618" s="10" t="n">
         <v>0</v>
@@ -23973,7 +23973,7 @@
         </is>
       </c>
       <c r="E619" s="6" t="n">
-        <v>-0.1865574311075713</v>
+        <v>-0.2406999714612764</v>
       </c>
       <c r="F619" s="6" t="n">
         <v>0.264961</v>
@@ -24010,7 +24010,7 @@
         </is>
       </c>
       <c r="E620" s="10" t="n">
-        <v>-0.834369785486845</v>
+        <v>-0.5144804881936289</v>
       </c>
       <c r="F620" s="10" t="n">
         <v>0.27967122</v>
@@ -24047,7 +24047,7 @@
         </is>
       </c>
       <c r="E621" s="6" t="n">
-        <v>-0.0602925729612508</v>
+        <v>-0.2068902181323879</v>
       </c>
       <c r="F621" s="6" t="n">
         <v>0.04402221</v>
@@ -24084,7 +24084,7 @@
         </is>
       </c>
       <c r="E622" s="10" t="n">
-        <v>0.7582842164007234</v>
+        <v>0.6093681425295293</v>
       </c>
       <c r="F622" s="10" t="n">
         <v>0.6402600000000001</v>
@@ -24121,7 +24121,7 @@
         </is>
       </c>
       <c r="E623" s="6" t="n">
-        <v>0.9777793497147892</v>
+        <v>0.241147691834776</v>
       </c>
       <c r="F623" s="6" t="n">
         <v>0</v>
@@ -24158,7 +24158,7 @@
         </is>
       </c>
       <c r="E624" s="10" t="n">
-        <v>-0.916591414212561</v>
+        <v>-1.252332687437555</v>
       </c>
       <c r="F624" s="10" t="n">
         <v>0.39812022</v>
@@ -24195,7 +24195,7 @@
         </is>
       </c>
       <c r="E625" s="6" t="n">
-        <v>-0.7926767427164109</v>
+        <v>-0.1418387966678991</v>
       </c>
       <c r="F625" s="6" t="n">
         <v>0</v>
@@ -24232,7 +24232,7 @@
         </is>
       </c>
       <c r="E626" s="10" t="n">
-        <v>0.9205721168075724</v>
+        <v>0.5516382451487566</v>
       </c>
       <c r="F626" s="10" t="n">
         <v>0</v>
@@ -24269,7 +24269,7 @@
         </is>
       </c>
       <c r="E627" s="6" t="n">
-        <v>-0.9973840673544974</v>
+        <v>-0.9878411635921096</v>
       </c>
       <c r="F627" s="6" t="n">
         <v>0</v>
@@ -24306,7 +24306,7 @@
         </is>
       </c>
       <c r="E628" s="10" t="n">
-        <v>-0.5560071121297604</v>
+        <v>-0.4317832093348952</v>
       </c>
       <c r="F628" s="10" t="n">
         <v>0.17926961</v>
@@ -24343,7 +24343,7 @@
         </is>
       </c>
       <c r="E629" s="6" t="n">
-        <v>0.3985761297456997</v>
+        <v>0.1362565661495127</v>
       </c>
       <c r="F629" s="6" t="n">
         <v>0</v>
@@ -24380,7 +24380,7 @@
         </is>
       </c>
       <c r="E630" s="10" t="n">
-        <v>-0.0155640859822675</v>
+        <v>0.0624564280568062</v>
       </c>
       <c r="F630" s="10" t="n">
         <v>0</v>
@@ -24417,7 +24417,7 @@
         </is>
       </c>
       <c r="E631" s="6" t="n">
-        <v>0.8969945052955784</v>
+        <v>0.9542282990205516</v>
       </c>
       <c r="F631" s="6" t="n">
         <v>0</v>
@@ -24454,7 +24454,7 @@
         </is>
       </c>
       <c r="E632" s="10" t="n">
-        <v>0.6415761723757978</v>
+        <v>0.7173036663551523</v>
       </c>
       <c r="F632" s="10" t="n">
         <v>0.80665773</v>
@@ -24491,7 +24491,7 @@
         </is>
       </c>
       <c r="E633" s="6" t="n">
-        <v>0.2228403081911624</v>
+        <v>-0.0506826774630403</v>
       </c>
       <c r="F633" s="6" t="n">
         <v>0.097524256</v>
@@ -24528,7 +24528,7 @@
         </is>
       </c>
       <c r="E634" s="10" t="n">
-        <v>0.4671678773343621</v>
+        <v>-0.0343682737765984</v>
       </c>
       <c r="F634" s="10" t="n">
         <v>0.35960212</v>
@@ -24565,7 +24565,7 @@
         </is>
       </c>
       <c r="E635" s="6" t="n">
-        <v>0.8372750504169907</v>
+        <v>0.1001261333218759</v>
       </c>
       <c r="F635" s="6" t="n">
         <v>0.8611547000000001</v>
@@ -24602,7 +24602,7 @@
         </is>
       </c>
       <c r="E636" s="10" t="n">
-        <v>-0.3672565320646768</v>
+        <v>-0.451524718367663</v>
       </c>
       <c r="F636" s="10" t="n">
         <v>0</v>
@@ -24639,7 +24639,7 @@
         </is>
       </c>
       <c r="E637" s="6" t="n">
-        <v>-0.3728864796332471</v>
+        <v>-0.4135441309243739</v>
       </c>
       <c r="F637" s="6" t="n">
         <v>0</v>
@@ -24676,7 +24676,7 @@
         </is>
       </c>
       <c r="E638" s="10" t="n">
-        <v>-0.3468115140739865</v>
+        <v>-0.1983995649405563</v>
       </c>
       <c r="F638" s="10" t="n">
         <v>0</v>
@@ -24713,7 +24713,7 @@
         </is>
       </c>
       <c r="E639" s="6" t="n">
-        <v>0.5733159177349015</v>
+        <v>0.2232342506654541</v>
       </c>
       <c r="F639" s="6" t="n">
         <v>0.71084505</v>
@@ -24750,7 +24750,7 @@
         </is>
       </c>
       <c r="E640" s="10" t="n">
-        <v>0.555396496889207</v>
+        <v>0.7860990592633829</v>
       </c>
       <c r="F640" s="10" t="n">
         <v>0</v>
@@ -24787,7 +24787,7 @@
         </is>
       </c>
       <c r="E641" s="6" t="n">
-        <v>0.3305079801854438</v>
+        <v>1.189778121727078</v>
       </c>
       <c r="F641" s="6" t="n">
         <v>0.1371723</v>
@@ -24824,7 +24824,7 @@
         </is>
       </c>
       <c r="E642" s="10" t="n">
-        <v>0.299201752872474</v>
+        <v>0.1220127065904118</v>
       </c>
       <c r="F642" s="10" t="n">
         <v>0.15156454</v>
@@ -24861,7 +24861,7 @@
         </is>
       </c>
       <c r="E643" s="6" t="n">
-        <v>-0.1116049308931932</v>
+        <v>-0.3791887316837203</v>
       </c>
       <c r="F643" s="6" t="n">
         <v>0.55610937</v>
@@ -24898,7 +24898,7 @@
         </is>
       </c>
       <c r="E644" s="10" t="n">
-        <v>0.2011270688959438</v>
+        <v>0.3992282056872203</v>
       </c>
       <c r="F644" s="10" t="n">
         <v>0</v>
@@ -24935,7 +24935,7 @@
         </is>
       </c>
       <c r="E645" s="6" t="n">
-        <v>0.4923381642708349</v>
+        <v>0.2797304926640944</v>
       </c>
       <c r="F645" s="6" t="n">
         <v>0.7889165</v>
@@ -24972,7 +24972,7 @@
         </is>
       </c>
       <c r="E646" s="10" t="n">
-        <v>-0.6545530202755745</v>
+        <v>-0.8391540952273657</v>
       </c>
       <c r="F646" s="10" t="n">
         <v>0</v>
@@ -25009,7 +25009,7 @@
         </is>
       </c>
       <c r="E647" s="6" t="n">
-        <v>0.6631264738837893</v>
+        <v>0.0810412625257529</v>
       </c>
       <c r="F647" s="6" t="n">
         <v>0</v>
@@ -25046,7 +25046,7 @@
         </is>
       </c>
       <c r="E648" s="10" t="n">
-        <v>1.128199072532584</v>
+        <v>1.582874412882924</v>
       </c>
       <c r="F648" s="10" t="n">
         <v>0.7277639</v>
@@ -25083,7 +25083,7 @@
         </is>
       </c>
       <c r="E649" s="6" t="n">
-        <v>0.466329910936787</v>
+        <v>-0.5685631371338148</v>
       </c>
       <c r="F649" s="6" t="n">
         <v>0</v>
@@ -25120,7 +25120,7 @@
         </is>
       </c>
       <c r="E650" s="10" t="n">
-        <v>-0.4733858027365487</v>
+        <v>-1.491010403864217</v>
       </c>
       <c r="F650" s="10" t="n">
         <v>0</v>
@@ -25157,7 +25157,7 @@
         </is>
       </c>
       <c r="E651" s="6" t="n">
-        <v>0.3608321498245878</v>
+        <v>-0.3860484923488458</v>
       </c>
       <c r="F651" s="6" t="n">
         <v>0</v>
@@ -25194,7 +25194,7 @@
         </is>
       </c>
       <c r="E652" s="10" t="n">
-        <v>-0.019738065795395</v>
+        <v>-0.2175706492475808</v>
       </c>
       <c r="F652" s="10" t="n">
         <v>0</v>
@@ -25231,7 +25231,7 @@
         </is>
       </c>
       <c r="E653" s="6" t="n">
-        <v>-0.2227082422279327</v>
+        <v>-0.2367183756651029</v>
       </c>
       <c r="F653" s="6" t="n">
         <v>0.50470436</v>
@@ -25268,7 +25268,7 @@
         </is>
       </c>
       <c r="E654" s="10" t="n">
-        <v>-0.2132140259460357</v>
+        <v>-0.9534125856555928</v>
       </c>
       <c r="F654" s="10" t="n">
         <v>0.63802165</v>
@@ -25305,7 +25305,7 @@
         </is>
       </c>
       <c r="E655" s="6" t="n">
-        <v>-0.6635047949346797</v>
+        <v>-0.8289486657066143</v>
       </c>
       <c r="F655" s="6" t="n">
         <v>0.20180841</v>
@@ -25342,7 +25342,7 @@
         </is>
       </c>
       <c r="E656" s="10" t="n">
-        <v>0.2856659384293792</v>
+        <v>-0.2462962586671326</v>
       </c>
       <c r="F656" s="10" t="n">
         <v>0</v>
@@ -25379,7 +25379,7 @@
         </is>
       </c>
       <c r="E657" s="6" t="n">
-        <v>0.0923373251328073</v>
+        <v>-0.2627178874364121</v>
       </c>
       <c r="F657" s="6" t="n">
         <v>0</v>
@@ -25416,7 +25416,7 @@
         </is>
       </c>
       <c r="E658" s="10" t="n">
-        <v>-0.8252586073805026</v>
+        <v>-0.2662269249530601</v>
       </c>
       <c r="F658" s="10" t="n">
         <v>0.07964691</v>
@@ -25453,7 +25453,7 @@
         </is>
       </c>
       <c r="E659" s="6" t="n">
-        <v>-0.6925867487415857</v>
+        <v>-0.9622025551851262</v>
       </c>
       <c r="F659" s="6" t="n">
         <v>0.08339509000000001</v>
@@ -25490,7 +25490,7 @@
         </is>
       </c>
       <c r="E660" s="10" t="n">
-        <v>-0.0350569523984297</v>
+        <v>-0.4578874726911153</v>
       </c>
       <c r="F660" s="10" t="n">
         <v>0.23437865</v>
@@ -25527,7 +25527,7 @@
         </is>
       </c>
       <c r="E661" s="6" t="n">
-        <v>0.4772615711459622</v>
+        <v>0.3962977845835457</v>
       </c>
       <c r="F661" s="6" t="n">
         <v>0</v>
@@ -25564,7 +25564,7 @@
         </is>
       </c>
       <c r="E662" s="10" t="n">
-        <v>0.6626131023177368</v>
+        <v>0.7728755757035987</v>
       </c>
       <c r="F662" s="10" t="n">
         <v>0.22162397</v>
@@ -25601,7 +25601,7 @@
         </is>
       </c>
       <c r="E663" s="6" t="n">
-        <v>-1.095787059261919</v>
+        <v>-0.8268940017069436</v>
       </c>
       <c r="F663" s="6" t="n">
         <v>0</v>
@@ -25638,7 +25638,7 @@
         </is>
       </c>
       <c r="E664" s="10" t="n">
-        <v>0.4825483315957211</v>
+        <v>1.064530840418913</v>
       </c>
       <c r="F664" s="10" t="n">
         <v>0</v>
@@ -25675,7 +25675,7 @@
         </is>
       </c>
       <c r="E665" s="6" t="n">
-        <v>0.0555501130506887</v>
+        <v>-0.3087033975336158</v>
       </c>
       <c r="F665" s="6" t="n">
         <v>0</v>
@@ -25712,7 +25712,7 @@
         </is>
       </c>
       <c r="E666" s="10" t="n">
-        <v>0.4584783899161782</v>
+        <v>-0.7293039848752514</v>
       </c>
       <c r="F666" s="10" t="n">
         <v>0.5118781</v>
@@ -25749,7 +25749,7 @@
         </is>
       </c>
       <c r="E667" s="6" t="n">
-        <v>0.624368801157288</v>
+        <v>-0.0691388998417525</v>
       </c>
       <c r="F667" s="6" t="n">
         <v>0.66131014</v>
@@ -25786,7 +25786,7 @@
         </is>
       </c>
       <c r="E668" s="10" t="n">
-        <v>0.3525670967401799</v>
+        <v>0.1431322104120529</v>
       </c>
       <c r="F668" s="10" t="n">
         <v>0</v>
@@ -25823,7 +25823,7 @@
         </is>
       </c>
       <c r="E669" s="6" t="n">
-        <v>0.266371622579665</v>
+        <v>0.3049697653773894</v>
       </c>
       <c r="F669" s="6" t="n">
         <v>0.70853907</v>
@@ -25860,7 +25860,7 @@
         </is>
       </c>
       <c r="E670" s="10" t="n">
-        <v>-0.2368793607059149</v>
+        <v>-0.1923632769366512</v>
       </c>
       <c r="F670" s="10" t="n">
         <v>0.28888243</v>
@@ -25897,7 +25897,7 @@
         </is>
       </c>
       <c r="E671" s="6" t="n">
-        <v>0.419363784589312</v>
+        <v>0.0287325855065962</v>
       </c>
       <c r="F671" s="6" t="n">
         <v>0.6887216</v>
@@ -25934,7 +25934,7 @@
         </is>
       </c>
       <c r="E672" s="10" t="n">
-        <v>-0.1373113088303637</v>
+        <v>-0.0299458770640962</v>
       </c>
       <c r="F672" s="10" t="n">
         <v>0.23755074</v>
@@ -25971,7 +25971,7 @@
         </is>
       </c>
       <c r="E673" s="6" t="n">
-        <v>-0.1742905188082539</v>
+        <v>-0.6647776368702562</v>
       </c>
       <c r="F673" s="6" t="n">
         <v>0.37810338</v>
@@ -26008,7 +26008,7 @@
         </is>
       </c>
       <c r="E674" s="10" t="n">
-        <v>0.7360193066421293</v>
+        <v>-0.1796262865449979</v>
       </c>
       <c r="F674" s="10" t="n">
         <v>0</v>
@@ -26045,7 +26045,7 @@
         </is>
       </c>
       <c r="E675" s="6" t="n">
-        <v>-0.3108448212373423</v>
+        <v>-0.7820808627326081</v>
       </c>
       <c r="F675" s="6" t="n">
         <v>0.110046685</v>
@@ -26082,7 +26082,7 @@
         </is>
       </c>
       <c r="E676" s="10" t="n">
-        <v>0.3361125442465272</v>
+        <v>0.3639443179430402</v>
       </c>
       <c r="F676" s="10" t="n">
         <v>0.09722944</v>
@@ -26119,7 +26119,7 @@
         </is>
       </c>
       <c r="E677" s="6" t="n">
-        <v>-0.3219993256817595</v>
+        <v>-0.7837494418674584</v>
       </c>
       <c r="F677" s="6" t="n">
         <v>0.5786356</v>
@@ -26156,7 +26156,7 @@
         </is>
       </c>
       <c r="E678" s="10" t="n">
-        <v>-0.5836179727600349</v>
+        <v>0.0224567066961365</v>
       </c>
       <c r="F678" s="10" t="n">
         <v>0.11876732</v>
@@ -26193,7 +26193,7 @@
         </is>
       </c>
       <c r="E679" s="6" t="n">
-        <v>-0.4773839867859457</v>
+        <v>-0.4335870529028009</v>
       </c>
       <c r="F679" s="6" t="n">
         <v>0.18586497</v>
@@ -26230,7 +26230,7 @@
         </is>
       </c>
       <c r="E680" s="10" t="n">
-        <v>0.0474657405993166</v>
+        <v>0.779346766516204</v>
       </c>
       <c r="F680" s="10" t="n">
         <v>0.80647075</v>
@@ -26267,7 +26267,7 @@
         </is>
       </c>
       <c r="E681" s="6" t="n">
-        <v>0.2831672124158327</v>
+        <v>-0.2286960783649862</v>
       </c>
       <c r="F681" s="6" t="n">
         <v>0.7140802000000001</v>
@@ -26304,7 +26304,7 @@
         </is>
       </c>
       <c r="E682" s="10" t="n">
-        <v>0.1132509775271248</v>
+        <v>-0.8401043868024467</v>
       </c>
       <c r="F682" s="10" t="n">
         <v>0.2287384</v>
@@ -26341,7 +26341,7 @@
         </is>
       </c>
       <c r="E683" s="6" t="n">
-        <v>0.4208054852364606</v>
+        <v>0.2340226230655195</v>
       </c>
       <c r="F683" s="6" t="n">
         <v>0.07848806</v>
@@ -26378,7 +26378,7 @@
         </is>
       </c>
       <c r="E684" s="10" t="n">
-        <v>-0.2678695438884431</v>
+        <v>-0.5119527439523058</v>
       </c>
       <c r="F684" s="10" t="n">
         <v>0.56332785</v>
@@ -26415,7 +26415,7 @@
         </is>
       </c>
       <c r="E685" s="6" t="n">
-        <v>0.6746412332004388</v>
+        <v>0.3173369979409015</v>
       </c>
       <c r="F685" s="6" t="n">
         <v>0.82086706</v>
@@ -26452,7 +26452,7 @@
         </is>
       </c>
       <c r="E686" s="10" t="n">
-        <v>-0.6659621314402359</v>
+        <v>-1.416833319390104</v>
       </c>
       <c r="F686" s="10" t="n">
         <v>0</v>
@@ -26489,7 +26489,7 @@
         </is>
       </c>
       <c r="E687" s="6" t="n">
-        <v>-0.3406494417857059</v>
+        <v>-1.055814643089897</v>
       </c>
       <c r="F687" s="6" t="n">
         <v>0</v>
@@ -26526,7 +26526,7 @@
         </is>
       </c>
       <c r="E688" s="10" t="n">
-        <v>0.6498477598570217</v>
+        <v>0.5648652421520928</v>
       </c>
       <c r="F688" s="10" t="n">
         <v>0</v>
@@ -26563,7 +26563,7 @@
         </is>
       </c>
       <c r="E689" s="6" t="n">
-        <v>-0.1876091250783872</v>
+        <v>-0.3232937317268305</v>
       </c>
       <c r="F689" s="6" t="n">
         <v>0.06876919400000001</v>
@@ -26600,7 +26600,7 @@
         </is>
       </c>
       <c r="E690" s="10" t="n">
-        <v>0.5374066031392691</v>
+        <v>0.3179230137159661</v>
       </c>
       <c r="F690" s="10" t="n">
         <v>0</v>
@@ -26637,7 +26637,7 @@
         </is>
       </c>
       <c r="E691" s="6" t="n">
-        <v>0.0179010476261329</v>
+        <v>0.7918302637222858</v>
       </c>
       <c r="F691" s="6" t="n">
         <v>0</v>
@@ -26674,7 +26674,7 @@
         </is>
       </c>
       <c r="E692" s="10" t="n">
-        <v>0.2448923008192295</v>
+        <v>1.23209327266039</v>
       </c>
       <c r="F692" s="10" t="n">
         <v>0.43794516</v>
@@ -26711,7 +26711,7 @@
         </is>
       </c>
       <c r="E693" s="6" t="n">
-        <v>1.050994349204593</v>
+        <v>1.054888667611887</v>
       </c>
       <c r="F693" s="6" t="n">
         <v>0</v>
@@ -26748,7 +26748,7 @@
         </is>
       </c>
       <c r="E694" s="10" t="n">
-        <v>-0.4994469687274163</v>
+        <v>0.6198306169170217</v>
       </c>
       <c r="F694" s="10" t="n">
         <v>0.77099925</v>
@@ -26785,7 +26785,7 @@
         </is>
       </c>
       <c r="E695" s="6" t="n">
-        <v>-0.3490266704661608</v>
+        <v>0.3732388003694997</v>
       </c>
       <c r="F695" s="6" t="n">
         <v>0.18794279</v>
@@ -26822,7 +26822,7 @@
         </is>
       </c>
       <c r="E696" s="10" t="n">
-        <v>0.4996097787642151</v>
+        <v>0.8068867543914084</v>
       </c>
       <c r="F696" s="10" t="n">
         <v>0.59627825</v>
@@ -26859,7 +26859,7 @@
         </is>
       </c>
       <c r="E697" s="6" t="n">
-        <v>0.3724609932382958</v>
+        <v>-0.063028699518895</v>
       </c>
       <c r="F697" s="6" t="n">
         <v>0</v>
@@ -26896,7 +26896,7 @@
         </is>
       </c>
       <c r="E698" s="10" t="n">
-        <v>0.2353659286826535</v>
+        <v>-0.1535069758559856</v>
       </c>
       <c r="F698" s="10" t="n">
         <v>0</v>
@@ -26933,7 +26933,7 @@
         </is>
       </c>
       <c r="E699" s="6" t="n">
-        <v>0.3578346343641527</v>
+        <v>0.4662388591087298</v>
       </c>
       <c r="F699" s="6" t="n">
         <v>0</v>
@@ -26970,7 +26970,7 @@
         </is>
       </c>
       <c r="E700" s="10" t="n">
-        <v>0.2345296613985341</v>
+        <v>-0.2122989847235853</v>
       </c>
       <c r="F700" s="10" t="n">
         <v>0.10252977</v>
@@ -27007,7 +27007,7 @@
         </is>
       </c>
       <c r="E701" s="6" t="n">
-        <v>0.1517730143415147</v>
+        <v>1.766623370628627</v>
       </c>
       <c r="F701" s="6" t="n">
         <v>0</v>
@@ -27044,7 +27044,7 @@
         </is>
       </c>
       <c r="E702" s="10" t="n">
-        <v>-0.1746955799646343</v>
+        <v>0.8187945604391865</v>
       </c>
       <c r="F702" s="10" t="n">
         <v>0</v>
@@ -27081,7 +27081,7 @@
         </is>
       </c>
       <c r="E703" s="6" t="n">
-        <v>-1.279179308032002</v>
+        <v>-1.192423686936152</v>
       </c>
       <c r="F703" s="6" t="n">
         <v>0</v>
@@ -27118,7 +27118,7 @@
         </is>
       </c>
       <c r="E704" s="10" t="n">
-        <v>-0.1577715567272779</v>
+        <v>1.098672614107969</v>
       </c>
       <c r="F704" s="10" t="n">
         <v>0.12666474</v>
@@ -27155,7 +27155,7 @@
         </is>
       </c>
       <c r="E705" s="6" t="n">
-        <v>-1.666515239126311</v>
+        <v>-0.2621894208437959</v>
       </c>
       <c r="F705" s="6" t="n">
         <v>0</v>
@@ -27192,7 +27192,7 @@
         </is>
       </c>
       <c r="E706" s="10" t="n">
-        <v>-0.5554423248488222</v>
+        <v>-0.7813741828347812</v>
       </c>
       <c r="F706" s="10" t="n">
         <v>0</v>
@@ -27229,7 +27229,7 @@
         </is>
       </c>
       <c r="E707" s="6" t="n">
-        <v>-0.4029833794521535</v>
+        <v>-0.4433092976734021</v>
       </c>
       <c r="F707" s="6" t="n">
         <v>0.72061986</v>
@@ -27266,7 +27266,7 @@
         </is>
       </c>
       <c r="E708" s="10" t="n">
-        <v>0.560889578392913</v>
+        <v>1.192124422264652</v>
       </c>
       <c r="F708" s="10" t="n">
         <v>0.62661344</v>
@@ -27303,7 +27303,7 @@
         </is>
       </c>
       <c r="E709" s="6" t="n">
-        <v>-0.6447458207927252</v>
+        <v>-1.18116959907458</v>
       </c>
       <c r="F709" s="6" t="n">
         <v>0</v>
@@ -27340,7 +27340,7 @@
         </is>
       </c>
       <c r="E710" s="10" t="n">
-        <v>-0.015818825211147</v>
+        <v>0.1256647592033105</v>
       </c>
       <c r="F710" s="10" t="n">
         <v>0</v>
@@ -27377,7 +27377,7 @@
         </is>
       </c>
       <c r="E711" s="6" t="n">
-        <v>-0.8113096603928605</v>
+        <v>-0.87223617774638</v>
       </c>
       <c r="F711" s="6" t="n">
         <v>0</v>
@@ -27414,7 +27414,7 @@
         </is>
       </c>
       <c r="E712" s="10" t="n">
-        <v>-0.5439797571173374</v>
+        <v>-0.9644807134170924</v>
       </c>
       <c r="F712" s="10" t="n">
         <v>0.31994745</v>
@@ -27451,7 +27451,7 @@
         </is>
       </c>
       <c r="E713" s="6" t="n">
-        <v>0.832349770915227</v>
+        <v>-0.0626316251693821</v>
       </c>
       <c r="F713" s="6" t="n">
         <v>0.5527484</v>
@@ -27488,7 +27488,7 @@
         </is>
       </c>
       <c r="E714" s="10" t="n">
-        <v>-0.3655374695497804</v>
+        <v>-1.026838673306127</v>
       </c>
       <c r="F714" s="10" t="n">
         <v>0.77895015</v>
@@ -27525,7 +27525,7 @@
         </is>
       </c>
       <c r="E715" s="6" t="n">
-        <v>0.6956486497466342</v>
+        <v>1.243744946325868</v>
       </c>
       <c r="F715" s="6" t="n">
         <v>0</v>
@@ -27562,7 +27562,7 @@
         </is>
       </c>
       <c r="E716" s="10" t="n">
-        <v>-1.308301881859425</v>
+        <v>-0.8159563908550033</v>
       </c>
       <c r="F716" s="10" t="n">
         <v>0</v>
@@ -27599,7 +27599,7 @@
         </is>
       </c>
       <c r="E717" s="6" t="n">
-        <v>-1.237876809338658</v>
+        <v>-1.134936557199956</v>
       </c>
       <c r="F717" s="6" t="n">
         <v>0</v>
@@ -27636,7 +27636,7 @@
         </is>
       </c>
       <c r="E718" s="10" t="n">
-        <v>-0.8619033077500604</v>
+        <v>-0.9047531338502124</v>
       </c>
       <c r="F718" s="10" t="n">
         <v>0.12981498</v>
@@ -27673,7 +27673,7 @@
         </is>
       </c>
       <c r="E719" s="6" t="n">
-        <v>-0.1181361464529658</v>
+        <v>0.0496720364205729</v>
       </c>
       <c r="F719" s="6" t="n">
         <v>0.8879214</v>
@@ -27710,7 +27710,7 @@
         </is>
       </c>
       <c r="E720" s="10" t="n">
-        <v>-0.1718357357474351</v>
+        <v>0.103326632514461</v>
       </c>
       <c r="F720" s="10" t="n">
         <v>0</v>
@@ -27747,7 +27747,7 @@
         </is>
       </c>
       <c r="E721" s="6" t="n">
-        <v>0.7564721054269944</v>
+        <v>1.175516790211764</v>
       </c>
       <c r="F721" s="6" t="n">
         <v>0</v>
@@ -27784,7 +27784,7 @@
         </is>
       </c>
       <c r="E722" s="10" t="n">
-        <v>0.5359104914948273</v>
+        <v>1.163130548297615</v>
       </c>
       <c r="F722" s="10" t="n">
         <v>0.10759501</v>
@@ -27821,7 +27821,7 @@
         </is>
       </c>
       <c r="E723" s="6" t="n">
-        <v>0.6823944756428352</v>
+        <v>1.544382272309694</v>
       </c>
       <c r="F723" s="6" t="n">
         <v>0</v>
@@ -27858,7 +27858,7 @@
         </is>
       </c>
       <c r="E724" s="10" t="n">
-        <v>-0.5494952589731995</v>
+        <v>-0.5709963219445783</v>
       </c>
       <c r="F724" s="10" t="n">
         <v>0</v>
@@ -27895,7 +27895,7 @@
         </is>
       </c>
       <c r="E725" s="6" t="n">
-        <v>0.3248778271985622</v>
+        <v>-0.5244202564012747</v>
       </c>
       <c r="F725" s="6" t="n">
         <v>0</v>
@@ -27932,7 +27932,7 @@
         </is>
       </c>
       <c r="E726" s="10" t="n">
-        <v>-0.9963718605334114</v>
+        <v>-1.150146016827538</v>
       </c>
       <c r="F726" s="10" t="n">
         <v>0</v>
@@ -27969,7 +27969,7 @@
         </is>
       </c>
       <c r="E727" s="6" t="n">
-        <v>0.6875359769740778</v>
+        <v>0.9138860065859014</v>
       </c>
       <c r="F727" s="6" t="n">
         <v>0</v>
@@ -28006,7 +28006,7 @@
         </is>
       </c>
       <c r="E728" s="10" t="n">
-        <v>-0.5257402649825288</v>
+        <v>-0.3188339372200881</v>
       </c>
       <c r="F728" s="10" t="n">
         <v>0.33119857</v>
@@ -28043,7 +28043,7 @@
         </is>
       </c>
       <c r="E729" s="6" t="n">
-        <v>0.19487292901532</v>
+        <v>-0.0017409342520368</v>
       </c>
       <c r="F729" s="6" t="n">
         <v>0</v>
@@ -28080,7 +28080,7 @@
         </is>
       </c>
       <c r="E730" s="10" t="n">
-        <v>0.6091648586114573</v>
+        <v>0.7673359109114505</v>
       </c>
       <c r="F730" s="10" t="n">
         <v>0.46013075</v>
@@ -28117,7 +28117,7 @@
         </is>
       </c>
       <c r="E731" s="6" t="n">
-        <v>1.064359987864056</v>
+        <v>-0.8943272839688733</v>
       </c>
       <c r="F731" s="6" t="n">
         <v>0.08576114</v>
@@ -28154,7 +28154,7 @@
         </is>
       </c>
       <c r="E732" s="10" t="n">
-        <v>-0.4760138881394256</v>
+        <v>-0.234131614085347</v>
       </c>
       <c r="F732" s="10" t="n">
         <v>0</v>
@@ -28191,7 +28191,7 @@
         </is>
       </c>
       <c r="E733" s="6" t="n">
-        <v>-0.5861282591541949</v>
+        <v>-0.6638935368076191</v>
       </c>
       <c r="F733" s="6" t="n">
         <v>0.13249631</v>
@@ -28228,7 +28228,7 @@
         </is>
       </c>
       <c r="E734" s="10" t="n">
-        <v>-0.3313712615341765</v>
+        <v>0.3113335629885422</v>
       </c>
       <c r="F734" s="10" t="n">
         <v>0</v>
@@ -28265,7 +28265,7 @@
         </is>
       </c>
       <c r="E735" s="6" t="n">
-        <v>0.4497442896880797</v>
+        <v>0.4377798808494323</v>
       </c>
       <c r="F735" s="6" t="n">
         <v>0</v>
@@ -28302,7 +28302,7 @@
         </is>
       </c>
       <c r="E736" s="10" t="n">
-        <v>1.493130877707133</v>
+        <v>0.9719219893170234</v>
       </c>
       <c r="F736" s="10" t="n">
         <v>0</v>
@@ -28339,7 +28339,7 @@
         </is>
       </c>
       <c r="E737" s="6" t="n">
-        <v>0.08986787268878341</v>
+        <v>0.5130780736588337</v>
       </c>
       <c r="F737" s="6" t="n">
         <v>0.55660075</v>
@@ -28376,7 +28376,7 @@
         </is>
       </c>
       <c r="E738" s="10" t="n">
-        <v>-0.6664170795555578</v>
+        <v>-0.3628571638877746</v>
       </c>
       <c r="F738" s="10" t="n">
         <v>0</v>
@@ -28413,7 +28413,7 @@
         </is>
       </c>
       <c r="E739" s="6" t="n">
-        <v>-0.362369461519559</v>
+        <v>0.4280732336789128</v>
       </c>
       <c r="F739" s="6" t="n">
         <v>0</v>
@@ -28450,7 +28450,7 @@
         </is>
       </c>
       <c r="E740" s="10" t="n">
-        <v>-0.6512936245557743</v>
+        <v>-0.1319824484608703</v>
       </c>
       <c r="F740" s="10" t="n">
         <v>0.4225748</v>
@@ -28487,7 +28487,7 @@
         </is>
       </c>
       <c r="E741" s="6" t="n">
-        <v>-0.6999475269366536</v>
+        <v>-0.8107826766462631</v>
       </c>
       <c r="F741" s="6" t="n">
         <v>0.06629984999999999</v>
@@ -28524,7 +28524,7 @@
         </is>
       </c>
       <c r="E742" s="10" t="n">
-        <v>-0.2068338023447209</v>
+        <v>-0.6086774165389607</v>
       </c>
       <c r="F742" s="10" t="n">
         <v>0.09124734</v>
@@ -28561,7 +28561,7 @@
         </is>
       </c>
       <c r="E743" s="6" t="n">
-        <v>-0.0268311808354529</v>
+        <v>0.63591959585942</v>
       </c>
       <c r="F743" s="6" t="n">
         <v>0.59009147</v>
@@ -28598,7 +28598,7 @@
         </is>
       </c>
       <c r="E744" s="10" t="n">
-        <v>-1.585118468034807</v>
+        <v>-0.9517857039055148</v>
       </c>
       <c r="F744" s="10" t="n">
         <v>0</v>
@@ -28635,7 +28635,7 @@
         </is>
       </c>
       <c r="E745" s="6" t="n">
-        <v>-0.8985362226047634</v>
+        <v>-1.467610993429623</v>
       </c>
       <c r="F745" s="6" t="n">
         <v>0</v>
@@ -28672,7 +28672,7 @@
         </is>
       </c>
       <c r="E746" s="10" t="n">
-        <v>-1.335359319086469</v>
+        <v>-0.8099584667409702</v>
       </c>
       <c r="F746" s="10" t="n">
         <v>0.08376196</v>
@@ -28709,7 +28709,7 @@
         </is>
       </c>
       <c r="E747" s="6" t="n">
-        <v>-0.0299838257109754</v>
+        <v>-0.1041544120483697</v>
       </c>
       <c r="F747" s="6" t="n">
         <v>0.3666082</v>
@@ -28746,7 +28746,7 @@
         </is>
       </c>
       <c r="E748" s="10" t="n">
-        <v>-1.51359235586352</v>
+        <v>-1.310164674282846</v>
       </c>
       <c r="F748" s="10" t="n">
         <v>0.66308033</v>
@@ -28783,7 +28783,7 @@
         </is>
       </c>
       <c r="E749" s="6" t="n">
-        <v>-0.1681515881605865</v>
+        <v>-1.471360750813349</v>
       </c>
       <c r="F749" s="6" t="n">
         <v>0</v>
@@ -28820,7 +28820,7 @@
         </is>
       </c>
       <c r="E750" s="10" t="n">
-        <v>-0.2114052231443785</v>
+        <v>1.195537962849508</v>
       </c>
       <c r="F750" s="10" t="n">
         <v>0</v>
@@ -28857,7 +28857,7 @@
         </is>
       </c>
       <c r="E751" s="6" t="n">
-        <v>-0.346971064105749</v>
+        <v>0.7201205874184082</v>
       </c>
       <c r="F751" s="6" t="n">
         <v>0.61389977</v>
@@ -28894,7 +28894,7 @@
         </is>
       </c>
       <c r="E752" s="10" t="n">
-        <v>-0.9177954719513119</v>
+        <v>-1.217632659575009</v>
       </c>
       <c r="F752" s="10" t="n">
         <v>0</v>
@@ -28931,7 +28931,7 @@
         </is>
       </c>
       <c r="E753" s="6" t="n">
-        <v>0.0456316315364359</v>
+        <v>0.07226907352251979</v>
       </c>
       <c r="F753" s="6" t="n">
         <v>0.16056198</v>
@@ -28968,7 +28968,7 @@
         </is>
       </c>
       <c r="E754" s="10" t="n">
-        <v>-0.2579345581623944</v>
+        <v>-0.1257649059556994</v>
       </c>
       <c r="F754" s="10" t="n">
         <v>0</v>
@@ -29005,7 +29005,7 @@
         </is>
       </c>
       <c r="E755" s="6" t="n">
-        <v>-0.5925958465299471</v>
+        <v>-0.5959664263216431</v>
       </c>
       <c r="F755" s="6" t="n">
         <v>0.14454438</v>
@@ -29042,7 +29042,7 @@
         </is>
       </c>
       <c r="E756" s="10" t="n">
-        <v>-0.6605298645725269</v>
+        <v>-1.345060061513184</v>
       </c>
       <c r="F756" s="10" t="n">
         <v>0.5862219</v>
@@ -29079,7 +29079,7 @@
         </is>
       </c>
       <c r="E757" s="6" t="n">
-        <v>0.7747962397572836</v>
+        <v>0.4136854514720121</v>
       </c>
       <c r="F757" s="6" t="n">
         <v>0</v>
@@ -29116,7 +29116,7 @@
         </is>
       </c>
       <c r="E758" s="10" t="n">
-        <v>1.535508662721312</v>
+        <v>0.1386902290051176</v>
       </c>
       <c r="F758" s="10" t="n">
         <v>0.09329612599999999</v>
@@ -29153,7 +29153,7 @@
         </is>
       </c>
       <c r="E759" s="6" t="n">
-        <v>0.5185985921725165</v>
+        <v>0.7829474157019068</v>
       </c>
       <c r="F759" s="6" t="n">
         <v>0.7398635</v>
@@ -29190,7 +29190,7 @@
         </is>
       </c>
       <c r="E760" s="10" t="n">
-        <v>-0.7228928477680268</v>
+        <v>-0.7933478131478466</v>
       </c>
       <c r="F760" s="10" t="n">
         <v>0</v>
@@ -29227,7 +29227,7 @@
         </is>
       </c>
       <c r="E761" s="6" t="n">
-        <v>-0.6427919376973721</v>
+        <v>-0.3301017722734261</v>
       </c>
       <c r="F761" s="6" t="n">
         <v>0.47842693</v>
@@ -29264,7 +29264,7 @@
         </is>
       </c>
       <c r="E762" s="10" t="n">
-        <v>0.3887140449392037</v>
+        <v>0.3154207972754597</v>
       </c>
       <c r="F762" s="10" t="n">
         <v>0.29881513</v>
@@ -29301,7 +29301,7 @@
         </is>
       </c>
       <c r="E763" s="6" t="n">
-        <v>0.9988981254117104</v>
+        <v>0.1487070841726753</v>
       </c>
       <c r="F763" s="6" t="n">
         <v>0.80324996</v>
@@ -29338,7 +29338,7 @@
         </is>
       </c>
       <c r="E764" s="10" t="n">
-        <v>0.1473567219932816</v>
+        <v>0.4814593354309673</v>
       </c>
       <c r="F764" s="10" t="n">
         <v>0</v>
@@ -29375,7 +29375,7 @@
         </is>
       </c>
       <c r="E765" s="6" t="n">
-        <v>0.5739963474319237</v>
+        <v>0.664029488363443</v>
       </c>
       <c r="F765" s="6" t="n">
         <v>0.7612189</v>
@@ -29412,7 +29412,7 @@
         </is>
       </c>
       <c r="E766" s="10" t="n">
-        <v>-0.1328864523957186</v>
+        <v>-0.2484519883357211</v>
       </c>
       <c r="F766" s="10" t="n">
         <v>0.3556816</v>
@@ -29449,7 +29449,7 @@
         </is>
       </c>
       <c r="E767" s="6" t="n">
-        <v>-0.8857701695122455</v>
+        <v>-1.318416746020254</v>
       </c>
       <c r="F767" s="6" t="n">
         <v>0</v>
@@ -29486,7 +29486,7 @@
         </is>
       </c>
       <c r="E768" s="10" t="n">
-        <v>0.0261806744425715</v>
+        <v>-0.357143125081219</v>
       </c>
       <c r="F768" s="10" t="n">
         <v>0</v>
@@ -29523,7 +29523,7 @@
         </is>
       </c>
       <c r="E769" s="6" t="n">
-        <v>-1.036990508603242</v>
+        <v>-0.4636150557560579</v>
       </c>
       <c r="F769" s="6" t="n">
         <v>0</v>
@@ -29560,7 +29560,7 @@
         </is>
       </c>
       <c r="E770" s="10" t="n">
-        <v>-0.3467803418012945</v>
+        <v>0.0130220067023518</v>
       </c>
       <c r="F770" s="10" t="n">
         <v>0</v>
@@ -29597,7 +29597,7 @@
         </is>
       </c>
       <c r="E771" s="6" t="n">
-        <v>0.2333890647029172</v>
+        <v>0.9596891075659932</v>
       </c>
       <c r="F771" s="6" t="n">
         <v>0</v>
@@ -29634,7 +29634,7 @@
         </is>
       </c>
       <c r="E772" s="10" t="n">
-        <v>-0.2499513556644165</v>
+        <v>-0.5338970337736647</v>
       </c>
       <c r="F772" s="10" t="n">
         <v>0</v>
@@ -29671,7 +29671,7 @@
         </is>
       </c>
       <c r="E773" s="6" t="n">
-        <v>-1.478717211992113</v>
+        <v>-1.220882403018305</v>
       </c>
       <c r="F773" s="6" t="n">
         <v>0</v>
@@ -29708,7 +29708,7 @@
         </is>
       </c>
       <c r="E774" s="10" t="n">
-        <v>-0.2147176451623059</v>
+        <v>-0.7927066894810314</v>
       </c>
       <c r="F774" s="10" t="n">
         <v>0.14041787</v>
@@ -29745,7 +29745,7 @@
         </is>
       </c>
       <c r="E775" s="6" t="n">
-        <v>0.9115556332679998</v>
+        <v>0.7347130659313114</v>
       </c>
       <c r="F775" s="6" t="n">
         <v>0.31443262</v>
@@ -29782,7 +29782,7 @@
         </is>
       </c>
       <c r="E776" s="10" t="n">
-        <v>-0.144670818678008</v>
+        <v>-1.091747040598176</v>
       </c>
       <c r="F776" s="10" t="n">
         <v>0</v>
@@ -29819,7 +29819,7 @@
         </is>
       </c>
       <c r="E777" s="6" t="n">
-        <v>-1.62141266065398</v>
+        <v>-0.7673247070144814</v>
       </c>
       <c r="F777" s="6" t="n">
         <v>0.21454307</v>
@@ -29856,7 +29856,7 @@
         </is>
       </c>
       <c r="E778" s="10" t="n">
-        <v>-1.136241849516767</v>
+        <v>-0.6252490020226911</v>
       </c>
       <c r="F778" s="10" t="n">
         <v>0.18670356</v>
@@ -29893,7 +29893,7 @@
         </is>
       </c>
       <c r="E779" s="6" t="n">
-        <v>-0.8258013572201387</v>
+        <v>-0.7922551700173178</v>
       </c>
       <c r="F779" s="6" t="n">
         <v>0</v>
@@ -29930,7 +29930,7 @@
         </is>
       </c>
       <c r="E780" s="10" t="n">
-        <v>-1.024864896392198</v>
+        <v>-0.838058096104859</v>
       </c>
       <c r="F780" s="10" t="n">
         <v>0.21238352</v>
@@ -29967,7 +29967,7 @@
         </is>
       </c>
       <c r="E781" s="6" t="n">
-        <v>0.130425492005509</v>
+        <v>0.5272531639102503</v>
       </c>
       <c r="F781" s="6" t="n">
         <v>0.53033334</v>
@@ -30004,7 +30004,7 @@
         </is>
       </c>
       <c r="E782" s="10" t="n">
-        <v>0.2592270414959607</v>
+        <v>-0.3882198110945742</v>
       </c>
       <c r="F782" s="10" t="n">
         <v>0</v>
@@ -30041,7 +30041,7 @@
         </is>
       </c>
       <c r="E783" s="6" t="n">
-        <v>-0.285236600594304</v>
+        <v>-0.6263039152634574</v>
       </c>
       <c r="F783" s="6" t="n">
         <v>0</v>
@@ -30078,7 +30078,7 @@
         </is>
       </c>
       <c r="E784" s="10" t="n">
-        <v>-0.0173255754727734</v>
+        <v>1.211744163582076</v>
       </c>
       <c r="F784" s="10" t="n">
         <v>0.07301154</v>
@@ -30115,7 +30115,7 @@
         </is>
       </c>
       <c r="E785" s="6" t="n">
-        <v>1.480652652896151</v>
+        <v>1.024870980371183</v>
       </c>
       <c r="F785" s="6" t="n">
         <v>0.6263566</v>
@@ -30152,7 +30152,7 @@
         </is>
       </c>
       <c r="E786" s="10" t="n">
-        <v>-1.354006972400299</v>
+        <v>-1.27764995113108</v>
       </c>
       <c r="F786" s="10" t="n">
         <v>0</v>
@@ -30189,7 +30189,7 @@
         </is>
       </c>
       <c r="E787" s="6" t="n">
-        <v>-0.1847246921863055</v>
+        <v>-0.5823547920842965</v>
       </c>
       <c r="F787" s="6" t="n">
         <v>0</v>
@@ -30226,7 +30226,7 @@
         </is>
       </c>
       <c r="E788" s="10" t="n">
-        <v>0.8253392247961617</v>
+        <v>2.190533446923817</v>
       </c>
       <c r="F788" s="10" t="n">
         <v>0</v>
@@ -30263,7 +30263,7 @@
         </is>
       </c>
       <c r="E789" s="6" t="n">
-        <v>1.131055970929184</v>
+        <v>0.2813813408897997</v>
       </c>
       <c r="F789" s="6" t="n">
         <v>0</v>
@@ -30300,7 +30300,7 @@
         </is>
       </c>
       <c r="E790" s="10" t="n">
-        <v>0.8924402580868089</v>
+        <v>1.324615199147094</v>
       </c>
       <c r="F790" s="10" t="n">
         <v>0.68494904</v>
@@ -30337,7 +30337,7 @@
         </is>
       </c>
       <c r="E791" s="6" t="n">
-        <v>0.1063258900555928</v>
+        <v>0.7643988417583764</v>
       </c>
       <c r="F791" s="6" t="n">
         <v>0</v>
@@ -30374,7 +30374,7 @@
         </is>
       </c>
       <c r="E792" s="10" t="n">
-        <v>-0.6503854317112352</v>
+        <v>-0.5779014172487836</v>
       </c>
       <c r="F792" s="10" t="n">
         <v>0.6944081</v>
